--- a/01_data/02_output/results_scientific_baseline.xlsx
+++ b/01_data/02_output/results_scientific_baseline.xlsx
@@ -56,7 +56,7 @@
     <t>01_data/01_input/251017_BioDYM_RyeCascading_System.xlsm</t>
   </si>
   <si>
-    <t>2025-10-18 15:59:21</t>
+    <t>2025-10-18 17:02:47</t>
   </si>
   <si>
     <t>2025 - 2050</t>
